--- a/Modules/CVMod8_V2/CVMod8_V2_BOM_THT.xlsx
+++ b/Modules/CVMod8_V2/CVMod8_V2_BOM_THT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\CVMod8_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9FCE47-716A-423C-8C89-69F770DB6416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4402B821-3F44-40B2-B486-B122A6C93FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,15 +164,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>M2 Screw</t>
   </si>
   <si>
@@ -455,9 +449,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.tme.eu/de/en/details/tfm-m2x10_dr211of/metal-spacers/dremec/211x10of/</t>
   </si>
   <si>
@@ -828,6 +819,15 @@
   </si>
   <si>
     <t>Avalon Harmonics CVMod8 V2 (THT)</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -1731,7 +1731,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1766,16 +1766,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>31</v>
@@ -1792,16 +1792,16 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -1813,19 +1813,19 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1836,19 +1836,19 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1868,10 +1868,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1885,13 +1885,13 @@
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>32</v>
@@ -1908,16 +1908,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1925,22 +1925,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
         <v>56</v>
       </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>58</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,22 +1948,22 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
         <v>60</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>57</v>
       </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>59</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1974,13 +1974,13 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>30</v>
@@ -1991,22 +1991,22 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2017,19 +2017,19 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2037,22 +2037,22 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2060,22 +2060,22 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2083,13 +2083,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -2098,7 +2098,7 @@
         <v>29</v>
       </c>
       <c r="J17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2106,22 +2106,22 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2135,16 +2135,16 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2152,22 +2152,22 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2178,19 +2178,19 @@
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2210,10 +2210,10 @@
         <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2221,19 +2221,19 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2241,19 +2241,19 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
         <v>69</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E25" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2261,19 +2261,19 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J26" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2281,19 +2281,19 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="C27" t="s">
+      <c r="F27" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="J27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2310,13 +2310,13 @@
         <v>42</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="J29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2324,19 +2324,19 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
         <v>42</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="J30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2356,7 +2356,7 @@
         <v>38</v>
       </c>
       <c r="J31" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2367,7 +2367,7 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s">
         <v>39</v>
@@ -2376,12 +2376,12 @@
         <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2389,27 +2389,27 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2434,28 +2434,28 @@
     <hyperlink ref="J8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="J3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="F31" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F29" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F30" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F32" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="J20" r:id="rId15" display="https://www.aliexpress.com/item/1005001557138121.html" xr:uid="{87917B98-45C2-4356-99DB-B5B8038C28A9}"/>
-    <hyperlink ref="F18" r:id="rId16" xr:uid="{7E9B1C1C-08C2-4E3A-836F-A55BD1AACB08}"/>
-    <hyperlink ref="J21" r:id="rId17" display="https://www.aliexpress.com/item/1005001557138121.html" xr:uid="{3932249F-F50C-48B7-B9ED-979BED78C705}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{617026E1-E8F8-41F0-B6F6-C7F3EABF9EDE}"/>
-    <hyperlink ref="F10" r:id="rId19" xr:uid="{D97E84B0-51EF-4445-A800-1CCE20EEB5DD}"/>
-    <hyperlink ref="F11" r:id="rId20" xr:uid="{37603052-44CC-44A4-A373-590BE7540B20}"/>
-    <hyperlink ref="F16" r:id="rId21" xr:uid="{57A67E62-1F07-4F81-BD71-0FCCC53DDD36}"/>
-    <hyperlink ref="F24" r:id="rId22" xr:uid="{386CA78F-ECAF-4BED-B017-86D6F4F05D83}"/>
-    <hyperlink ref="F25" r:id="rId23" xr:uid="{23053745-F5D1-4E91-88AD-FDB570AEC8C5}"/>
-    <hyperlink ref="F27" r:id="rId24" xr:uid="{3EC41E3D-44DB-45CF-A556-8137102A88B8}"/>
-    <hyperlink ref="F15" r:id="rId25" xr:uid="{11ED5ED0-56A5-4C20-93A1-FDAE72827046}"/>
-    <hyperlink ref="F22" r:id="rId26" xr:uid="{A893ABC8-5223-47F2-8335-C8AD6F9E7D68}"/>
-    <hyperlink ref="F4" r:id="rId27" xr:uid="{D1B00FCF-CFA9-4559-AFDD-E930832032EF}"/>
-    <hyperlink ref="F13" r:id="rId28" xr:uid="{29AEA817-32F1-41F4-A924-4F4000D4818B}"/>
-    <hyperlink ref="F3" r:id="rId29" xr:uid="{8A7A5D82-A3F8-44CA-BA5B-9240FAD7EA78}"/>
-    <hyperlink ref="F8" r:id="rId30" xr:uid="{5987D41B-D98C-45BC-A0CC-34272D97726E}"/>
-    <hyperlink ref="F21" r:id="rId31" xr:uid="{8E872B71-2423-4E3E-A4A8-BAD79ACAED0B}"/>
-    <hyperlink ref="F20" r:id="rId32" xr:uid="{7AFABD24-8F23-415C-8FB0-53C856BB2EE7}"/>
-    <hyperlink ref="F26" r:id="rId33" xr:uid="{43A1E3D1-40BA-485C-A829-B483D6181C61}"/>
+    <hyperlink ref="F32" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="J20" r:id="rId13" display="https://www.aliexpress.com/item/1005001557138121.html" xr:uid="{87917B98-45C2-4356-99DB-B5B8038C28A9}"/>
+    <hyperlink ref="F18" r:id="rId14" xr:uid="{7E9B1C1C-08C2-4E3A-836F-A55BD1AACB08}"/>
+    <hyperlink ref="J21" r:id="rId15" display="https://www.aliexpress.com/item/1005001557138121.html" xr:uid="{3932249F-F50C-48B7-B9ED-979BED78C705}"/>
+    <hyperlink ref="F19" r:id="rId16" xr:uid="{617026E1-E8F8-41F0-B6F6-C7F3EABF9EDE}"/>
+    <hyperlink ref="F10" r:id="rId17" xr:uid="{D97E84B0-51EF-4445-A800-1CCE20EEB5DD}"/>
+    <hyperlink ref="F11" r:id="rId18" xr:uid="{37603052-44CC-44A4-A373-590BE7540B20}"/>
+    <hyperlink ref="F16" r:id="rId19" xr:uid="{57A67E62-1F07-4F81-BD71-0FCCC53DDD36}"/>
+    <hyperlink ref="F24" r:id="rId20" xr:uid="{386CA78F-ECAF-4BED-B017-86D6F4F05D83}"/>
+    <hyperlink ref="F25" r:id="rId21" xr:uid="{23053745-F5D1-4E91-88AD-FDB570AEC8C5}"/>
+    <hyperlink ref="F27" r:id="rId22" xr:uid="{3EC41E3D-44DB-45CF-A556-8137102A88B8}"/>
+    <hyperlink ref="F15" r:id="rId23" xr:uid="{11ED5ED0-56A5-4C20-93A1-FDAE72827046}"/>
+    <hyperlink ref="F4" r:id="rId24" xr:uid="{D1B00FCF-CFA9-4559-AFDD-E930832032EF}"/>
+    <hyperlink ref="F13" r:id="rId25" xr:uid="{29AEA817-32F1-41F4-A924-4F4000D4818B}"/>
+    <hyperlink ref="F3" r:id="rId26" xr:uid="{8A7A5D82-A3F8-44CA-BA5B-9240FAD7EA78}"/>
+    <hyperlink ref="F8" r:id="rId27" xr:uid="{5987D41B-D98C-45BC-A0CC-34272D97726E}"/>
+    <hyperlink ref="F21" r:id="rId28" xr:uid="{8E872B71-2423-4E3E-A4A8-BAD79ACAED0B}"/>
+    <hyperlink ref="F20" r:id="rId29" xr:uid="{7AFABD24-8F23-415C-8FB0-53C856BB2EE7}"/>
+    <hyperlink ref="F26" r:id="rId30" xr:uid="{43A1E3D1-40BA-485C-A829-B483D6181C61}"/>
+    <hyperlink ref="F29" r:id="rId31" xr:uid="{F8AF0FCA-D55C-489E-95EF-5A29E88E1C42}"/>
+    <hyperlink ref="F30" r:id="rId32" xr:uid="{A42CDDBD-9EBF-482C-934F-1A90DBC98365}"/>
+    <hyperlink ref="F22" r:id="rId33" xr:uid="{5025E765-5D10-4B70-AD8F-EA2847A5B5D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
